--- a/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
+++ b/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{454DB34A-6966-4E3E-BEAC-0EAD0066D3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB89C829-E49A-4AA1-AAD3-4011BB9528FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Global Search User</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Time Record Manager</t>
+  </si>
+  <si>
+    <t>115826</t>
   </si>
 </sst>
 </file>
@@ -882,26 +885,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -910,6 +913,9 @@
       </c>
       <c r="C2" t="s">
         <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
+++ b/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB89C829-E49A-4AA1-AAD3-4011BB9528FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0052049-B48D-4DF6-BDC6-109F6E44E56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Global Search User</t>
   </si>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>115826</t>
+  </si>
+  <si>
+    <t>Time Tracking Beta Supervisor</t>
+  </si>
+  <si>
+    <t>GroupNam</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>CAO</t>
   </si>
 </sst>
 </file>
@@ -819,34 +831,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA9779A-E3DE-42CF-890B-727C0A1D4E98}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA9779A-E3DE-42CF-890B-727C0A1D4E98}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
+++ b/TestData/LV_TMTT0011419_VerifyTASSupervisorCanonlyEnterLessThan24HoursForOneDayforAssociatesLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CA46A4-0AEC-4BCE-A389-EF7BB5256653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0052049-B48D-4DF6-BDC6-109F6E44E56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="8" r:id="rId1"/>
@@ -47,6 +47,9 @@
     <t>Staff Member</t>
   </si>
   <si>
+    <t>Alexander Drews</t>
+  </si>
+  <si>
     <t>Activity Selection</t>
   </si>
   <si>
@@ -120,9 +123,6 @@
   </si>
   <si>
     <t>CAO</t>
-  </si>
-  <si>
-    <t>Michael Goldstein</t>
   </si>
 </sst>
 </file>
@@ -832,32 +832,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -868,19 +868,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA9779A-E3DE-42CF-890B-727C0A1D4E98}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -891,19 +891,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CB5A968-CB96-4001-8EAB-8A3A897E5B2F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -914,36 +914,36 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -955,19 +955,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -978,19 +978,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1001,26 +1001,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1031,25 +1031,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1060,19 +1060,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
